--- a/bottle/藥劑清單.xlsx
+++ b/bottle/藥劑清單.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ken88\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ken88\Desktop\medicine_bottle\bottle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87CB306-91B3-4603-AB13-249F80C56EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79B4606-7984-4879-860F-BAB9EA9954FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="17496" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27132" yWindow="3012" windowWidth="23040" windowHeight="12660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Syring" sheetId="1" r:id="rId1"/>
@@ -133,10 +133,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ROLIKAN INJECTION (SODIUM BICARBONATE))</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>https://www.kingnet.com.tw/medicine/merchandise?license_id=%E8%A1%9B%E7%BD%B2%E8%97%A5%E8%A3%BD%E5%AD%97%E7%AC%AC027456%E8%99%9F</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -210,6 +206,10 @@
   </si>
   <si>
     <t>MILLISROL INJECTION</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ROLIKAN INJECTION (SODIUM BICARBONATE)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1094,10 +1094,10 @@
         <v>26</v>
       </c>
       <c r="D7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>27</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1169,13 +1169,13 @@
         <v>4711457371105</v>
       </c>
       <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
         <v>29</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1194,6 +1194,7 @@
     <hyperlink ref="E3" r:id="rId2" xr:uid="{20A6809E-DAAB-4211-8114-3C7AE6667FEB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -1233,13 +1234,13 @@
         <v>4710596702344</v>
       </c>
       <c r="C2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" t="s">
         <v>33</v>
       </c>
-      <c r="D2" t="s">
-        <v>34</v>
-      </c>
       <c r="E2" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1250,13 +1251,13 @@
         <v>4719858033455</v>
       </c>
       <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
         <v>36</v>
       </c>
-      <c r="D3" t="s">
-        <v>37</v>
-      </c>
       <c r="E3" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -1267,13 +1268,13 @@
         <v>108806520004816</v>
       </c>
       <c r="C4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s">
         <v>39</v>
       </c>
-      <c r="D4" t="s">
-        <v>40</v>
-      </c>
       <c r="E4" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -1290,7 +1291,8 @@
     <hyperlink ref="E4" r:id="rId3" xr:uid="{4937471F-BA7E-4BFC-B9CA-7D12471D8D50}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -1331,13 +1333,13 @@
         <v>4715550032017</v>
       </c>
       <c r="C2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" t="s">
         <v>42</v>
       </c>
-      <c r="D2" t="s">
-        <v>43</v>
-      </c>
       <c r="E2" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1348,13 +1350,13 @@
         <v>4987170870854</v>
       </c>
       <c r="C3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" t="s">
         <v>45</v>
       </c>
-      <c r="D3" t="s">
-        <v>46</v>
-      </c>
       <c r="E3" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1364,5 +1366,6 @@
     <hyperlink ref="E3" r:id="rId2" xr:uid="{DCF29834-64BE-411B-B120-091107157FD2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>